--- a/archive/InnovateUK_Funding_Opportunities_WeeklyBreakdown_2026-02-24.xlsx
+++ b/archive/InnovateUK_Funding_Opportunities_WeeklyBreakdown_2026-02-24.xlsx
@@ -481,13 +481,13 @@
         <v>46071</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -7728,7 +7728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8090,26 +8090,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>iX Challenge - Enabling regional carbon dioxide utilisation in Southwest Wales through geospatial intelligence</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/ix-challenge-enabling-regional-carbon-dioxide-utilisation-southwest-wales/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-24 10:36</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46073.43888888889</v>
+        <v>46077.44166666667</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -8118,25 +8118,190 @@
       <c r="H7" t="b">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>46077</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>23/04/2026                              23:59</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>46113.45833333334</v>
+        <v>46135.99930555555</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N7" s="2" t="n">
         <v>46071</v>
       </c>
       <c r="O7" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Semiconductors and components for smart electronic platforms</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:32</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46073.43888888889</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Wednesday 1 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Hubs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:43</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46077.44652777778</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>£7.5 million</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Robotics Adoption Central Convening Body</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:43</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46077.44652777778</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Wednesday 15 April 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>46127.45833333334</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>46071</v>
       </c>
     </row>
